--- a/test/fixtures/xlsx/composite-expanded/composite-expanded.xlsx
+++ b/test/fixtures/xlsx/composite-expanded/composite-expanded.xlsx
@@ -12,38 +12,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="53">
-  <si>
-    <t xml:space="preserve">~~table:Vectors~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="56">
+  <si>
+    <t xml:space="preserve">:table Vectors</t>
   </si>
   <si>
     <t xml:space="preserve">Vectors, a rotation and two colours, in one notation or the other.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">Pos.X</t>
   </si>
   <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
     <t xml:space="preserve">where it is</t>
   </si>
   <si>
-    <t xml:space="preserve">float</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pos.Y</t>
   </si>
   <si>
@@ -107,10 +116,10 @@
     <t xml:space="preserve">Label</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">a plain column after the components</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -215,140 +224,206 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:T11"/>
+  <dimension ref="B2:U9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="P4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="R4" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="S4" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="T4" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="U4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T5" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="U5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -360,10 +435,10 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -378,16 +453,16 @@
         <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P6" t="s">
         <v>9</v>
@@ -402,145 +477,145 @@
         <v>9</v>
       </c>
       <c r="T6" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="U6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="J7" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="P7" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="R7" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="S7" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>5</v>
+        <v>36</v>
+      </c>
+      <c r="U7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="M8" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="N8" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="P8" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="Q8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="R8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="S8" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="T8" t="s">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="U8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
@@ -549,155 +624,40 @@
         <v>36</v>
       </c>
       <c r="J9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L9" t="s">
         <v>39</v>
       </c>
       <c r="M9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="S9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K10" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" t="s">
-        <v>49</v>
-      </c>
-      <c r="O10" t="s">
-        <v>42</v>
-      </c>
-      <c r="P10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>36</v>
-      </c>
-      <c r="R10" t="s">
-        <v>36</v>
-      </c>
-      <c r="S10" t="s">
-        <v>36</v>
-      </c>
-      <c r="T10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" t="s">
-        <v>36</v>
-      </c>
-      <c r="O11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P11" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>36</v>
-      </c>
-      <c r="R11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" t="s">
-        <v>52</v>
+        <v>36</v>
+      </c>
+      <c r="U9" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
